--- a/data/trans_camb/P32A-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P32A-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 4,02</t>
+          <t>0,3; 3,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 2,52</t>
+          <t>-0,3; 2,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,57</t>
+          <t>0,28; 3,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,42</t>
+          <t>0,0; 3,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,94</t>
+          <t>0,0; 5,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,49</t>
+          <t>0,09; 3,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,75</t>
+          <t>0,37; 3,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,94</t>
+          <t>0,0; 2,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,9</t>
+          <t>0,43; 2,67</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 3,59</t>
+          <t>-1,94; 3,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 2,11</t>
+          <t>-2,35; 1,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 0,96</t>
+          <t>-2,6; 1,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,03</t>
+          <t>0,0; 5,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,63</t>
+          <t>0,59; 5,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,78</t>
+          <t>0,75; 5,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 2,61</t>
+          <t>-0,8; 2,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 2,39</t>
+          <t>-0,65; 2,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,74</t>
+          <t>-0,85; 1,76</t>
         </is>
       </c>
     </row>
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-83,27; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-74,07; 843,25</t>
+          <t>-59,81; 975,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-67,84; inf</t>
+          <t>-68,21; 717,97</t>
         </is>
       </c>
     </row>
@@ -1109,17 +1109,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 4,97</t>
+          <t>-0,16; 4,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 3,28</t>
+          <t>-1,01; 2,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 3,09</t>
+          <t>-1,12; 2,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,76</t>
+          <t>0,0; 10,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1139,17 +1139,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 3,99</t>
+          <t>-0,04; 4,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 2,98</t>
+          <t>-0,57; 3,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 2,58</t>
+          <t>-1,1; 2,48</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-20,55; 1027,61</t>
+          <t>-21,39; 890,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-60,56; 649,03</t>
+          <t>-57,4; 504,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-75,48; 526,76</t>
+          <t>-71,55; 488,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-23,19; 927,76</t>
+          <t>-31,19; 827,96</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-41,66; 634,92</t>
+          <t>-48,29; 731,76</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-70,31; 667,53</t>
+          <t>-74,01; 510,55</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 2,61</t>
+          <t>-0,55; 2,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 1,63</t>
+          <t>-1,02; 1,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 2,61</t>
+          <t>-0,71; 2,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,56</t>
+          <t>0,0; 2,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 1,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 2,1</t>
+          <t>0,04; 1,93</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 1,97</t>
+          <t>-0,29; 2,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,2</t>
+          <t>-0,85; 1,2</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 1,71</t>
+          <t>-0,74; 1,77</t>
         </is>
       </c>
     </row>
@@ -1431,17 +1431,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-35,31; 300,51</t>
+          <t>-32,54; 312,18</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-61,85; 203,97</t>
+          <t>-56,3; 281,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-41,35; 293,98</t>
+          <t>-43,45; 305,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-35,05; 298,27</t>
+          <t>-32,68; 370,39</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-59,2; 191,56</t>
+          <t>-54,6; 219,8</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-51,98; 250,05</t>
+          <t>-53,24; 286,61</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 4,26</t>
+          <t>-0,05; 4,3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,19; 5,31</t>
+          <t>0,23; 5,22</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 3,58</t>
+          <t>-0,69; 3,69</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 2,07</t>
+          <t>-3,28; 1,76</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 0,59</t>
+          <t>-4,05; 0,84</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 2,87</t>
+          <t>-2,4; 2,78</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 2,94</t>
+          <t>-0,75; 2,72</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 3,1</t>
+          <t>-0,55; 3,28</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 2,58</t>
+          <t>-0,69; 2,62</t>
         </is>
       </c>
     </row>
@@ -1647,17 +1647,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-52,11; —</t>
+          <t>-53,64; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-31,81; —</t>
+          <t>-22,61; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-68,44; —</t>
+          <t>-66,97; —</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1672,22 +1672,22 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-30,23; 873,58</t>
+          <t>-49,3; 701,95</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-43,84; 798,27</t>
+          <t>-45,03; 754,76</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-52,52; 694,59</t>
+          <t>-44,84; 664,39</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,66; 6,91</t>
+          <t>0,69; 6,38</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,75</t>
+          <t>0,65; 6,13</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1772,32 +1772,32 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 3,03</t>
+          <t>-0,93; 3,13</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 3,72</t>
+          <t>-0,24; 3,68</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 8,85</t>
+          <t>-0,92; 9,04</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,18; 3,24</t>
+          <t>0,15; 3,49</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,83</t>
+          <t>0,61; 3,68</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 4,8</t>
+          <t>-0,56; 4,54</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,41</t>
+          <t>0,64; 2,41</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,74</t>
+          <t>0,13; 1,74</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 1,52</t>
+          <t>-0,07; 1,46</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 1,3</t>
+          <t>-0,09; 1,37</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,91</t>
+          <t>0,35; 1,89</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,83</t>
+          <t>0,15; 1,95</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,76</t>
+          <t>0,55; 1,74</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,51</t>
+          <t>0,42; 1,57</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,36</t>
+          <t>0,15; 1,38</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>32,77; 319,73</t>
+          <t>42,6; 310,95</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 224,02</t>
+          <t>5,9; 222,42</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-12,2; 198,06</t>
+          <t>-8,35; 195,45</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-57,89; 1388,25</t>
+          <t>-41,88; —</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,75; 1517,62</t>
+          <t>21,59; 1637,43</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 1438,19</t>
+          <t>-10,5; 1500,37</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>48,05; 297,24</t>
+          <t>47,04; 295,66</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>30,49; 251,79</t>
+          <t>36,62; 276,82</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3,21; 210,34</t>
+          <t>10,33; 224,36</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P32A-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P32A-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,56</t>
+          <t>1,79</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,39</t>
+          <t>1,33</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,49</t>
+          <t>1,61</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,77</t>
+          <t>0,26; 3,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 2,48</t>
+          <t>-0,32; 2,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,46</t>
+          <t>0,46; 3,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,1</t>
+          <t>0,0; 3,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,97</t>
+          <t>0,0; 6,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 3,9</t>
+          <t>0,31; 3,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,0</t>
+          <t>0,37; 2,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,82</t>
+          <t>0,18; 2,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,67</t>
+          <t>0,56; 3,09</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>490,69%</t>
+          <t>561,83%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>670,15%</t>
+          <t>725,28%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,56</t>
+          <t>-0,23</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,07</t>
+          <t>2,82</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>0,98</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 3,33</t>
+          <t>-1,88; 3,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 1,84</t>
+          <t>-2,45; 2,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 1,04</t>
+          <t>-2,78; 1,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,95</t>
+          <t>0,0; 3,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,5</t>
+          <t>0,58; 5,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 5,47</t>
+          <t>1,08; 5,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 2,83</t>
+          <t>-0,76; 3,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 2,64</t>
+          <t>-0,63; 2,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 1,76</t>
+          <t>-0,59; 2,41</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-40,33%</t>
+          <t>-16,87%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>119,96%</t>
         </is>
       </c>
     </row>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-59,81; 975,94</t>
+          <t>-57,3; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-68,21; 717,97</t>
+          <t>-45,35; —</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,64</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,53</t>
+          <t>0,37</t>
         </is>
       </c>
     </row>
@@ -1109,17 +1109,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 4,79</t>
+          <t>-0,05; 5,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 2,98</t>
+          <t>-0,83; 3,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 2,92</t>
+          <t>-1,31; 2,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,48</t>
+          <t>0,0; 10,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1139,17 +1139,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 4,0</t>
+          <t>-0,15; 3,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 3,14</t>
+          <t>-0,59; 2,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 2,48</t>
+          <t>-1,17; 2,0</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>31,89%</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-21,39; 890,23</t>
+          <t>-23,78; 823,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-57,4; 504,41</t>
+          <t>-51,53; 517,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-71,55; 488,38</t>
+          <t>-78,14; 494,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-31,19; 827,96</t>
+          <t>-25,75; 808,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-48,29; 731,76</t>
+          <t>-53,78; 621,54</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-74,01; 510,55</t>
+          <t>-75,29; 397,09</t>
         </is>
       </c>
     </row>
@@ -1282,29 +1282,29 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>0,71</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0,85</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,37</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,86</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
           <t>0,86</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,85</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,37</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,69</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,86</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
           <t>0,19</t>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,47</t>
+          <t>1,25</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 2,52</t>
+          <t>-0,49; 2,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,81</t>
+          <t>-1,1; 1,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 2,46</t>
+          <t>-0,68; 2,31</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,57</t>
+          <t>0,0; 2,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,88</t>
+          <t>0,0; 2,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,04; 1,93</t>
+          <t>1,01; 7,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 2,27</t>
+          <t>-0,31; 2,08</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 1,2</t>
+          <t>-0,81; 1,3</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,77</t>
+          <t>0,07; 2,86</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>114,1%</t>
         </is>
       </c>
     </row>
@@ -1431,17 +1431,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-32,54; 312,18</t>
+          <t>-29,7; 346,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-56,3; 281,54</t>
+          <t>-57,53; 239,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-43,45; 305,77</t>
+          <t>-38,38; 262,19</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-32,68; 370,39</t>
+          <t>-28,89; 370,06</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-54,6; 219,8</t>
+          <t>-54,42; 208,88</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-53,24; 286,61</t>
+          <t>-2,03; 503,54</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,23</t>
+          <t>1,0</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,52</t>
+          <t>0,32</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>0,74</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 4,3</t>
+          <t>-0,06; 4,48</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,23; 5,22</t>
+          <t>0,31; 5,29</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 3,69</t>
+          <t>-1,14; 2,95</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 1,76</t>
+          <t>-3,56; 2,02</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 0,84</t>
+          <t>-4,02; 1,07</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 2,78</t>
+          <t>-2,52; 2,52</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 2,72</t>
+          <t>-0,57; 2,83</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 3,28</t>
+          <t>-0,45; 3,1</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 2,62</t>
+          <t>-0,78; 2,2</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>129,03%</t>
+          <t>105,12%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>65,73%</t>
         </is>
       </c>
     </row>
@@ -1647,17 +1647,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-53,64; —</t>
+          <t>-47,29; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-22,61; —</t>
+          <t>-31,77; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-66,97; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1672,29 +1672,29 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-88,18; —</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-49,3; 701,95</t>
+          <t>-44,53; 612,48</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-45,03; 754,76</t>
+          <t>-40,92; 703,55</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-44,84; 664,39</t>
+          <t>-48,79; 553,65</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,37</t>
+          <t>1,29</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>0,76</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,69; 6,38</t>
+          <t>0,66; 6,29</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,65; 6,13</t>
+          <t>0,65; 6,12</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1772,32 +1772,32 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 3,13</t>
+          <t>-0,93; 3,06</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 3,68</t>
+          <t>-0,11; 3,61</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 9,04</t>
+          <t>-0,93; 8,67</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,15; 3,49</t>
+          <t>0,34; 3,22</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,68</t>
+          <t>0,64; 3,66</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 4,54</t>
+          <t>-0,29; 5,05</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>293,24%</t>
+          <t>276,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>261,96%</t>
+          <t>268,1%</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>1,7</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>1,05</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,41</t>
+          <t>0,6; 2,31</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,74</t>
+          <t>0,13; 1,71</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 1,46</t>
+          <t>-0,03; 1,5</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 1,37</t>
+          <t>-0,15; 1,39</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,89</t>
+          <t>0,32; 1,95</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,95</t>
+          <t>0,76; 3,04</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,74</t>
+          <t>0,55; 1,75</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,57</t>
+          <t>0,32; 1,5</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,38</t>
+          <t>0,46; 1,73</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>278,79%</t>
+          <t>514,59%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>126,76%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>42,6; 310,95</t>
+          <t>39,63; 301,67</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>5,9; 222,42</t>
+          <t>4,34; 224,17</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 195,45</t>
+          <t>-3,55; 194,58</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-41,88; —</t>
+          <t>-48,51; 1161,69</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>21,59; 1637,43</t>
+          <t>20,8; 1721,59</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-10,5; 1500,37</t>
+          <t>74,59; 2258,79</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>47,04; 295,66</t>
+          <t>46,66; 281,09</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>36,62; 276,82</t>
+          <t>27,2; 244,34</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>10,33; 224,36</t>
+          <t>39,99; 276,8</t>
         </is>
       </c>
     </row>
